--- a/templates/research_template.xlsx
+++ b/templates/research_template.xlsx
@@ -2959,7 +2959,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="521">
   <si>
     <r>
       <rPr>
@@ -8725,6 +8725,314 @@
       </rPr>
       <t xml:space="preserve">법률 안내</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">copyright_import</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">저작권법 제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">124</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">조</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">침해로 보는 수입</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에 해당하는가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">국내 저작권자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">라이선시 허락 없는 수입</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">변리사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">변호사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">한국저작권위원회</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">design_right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">국내 등록 디자인과 유사한 형상인가</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">KIPRIS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">디자인 검색</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">customs_ip_watch</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">권리자가 세관에 지재권 신고를 해 두었는가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">통관보류 위험</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">관세청 지재권 신고 조회</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">관세사</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">platform_ip_report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">채널 지재권 신고 시 정품 소명 자료를 낼 수 있는가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">네이버 지식재산권보호센터</t>
+  </si>
+  <si>
+    <t xml:space="preserve">listing_assets</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상세페이지 이미지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">문구 사용권이 있는가</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">직접 촬영 예정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">조건부</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">판매자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공식 이미지 무단 사용 금지</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">자체</t>
   </si>
   <si>
     <t xml:space="preserve">customs</t>
@@ -12090,31 +12398,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>404</v>
+        <v>422</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>33</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>406</v>
+        <v>424</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>407</v>
+        <v>425</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>408</v>
+        <v>426</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="J1" s="6" t="s">
         <v>42</v>
@@ -12122,75 +12430,75 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>410</v>
+        <v>428</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="8" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="J2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>49</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="8" t="s">
-        <v>419</v>
+        <v>437</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="J3" s="7"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>422</v>
+        <v>440</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>49</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
@@ -12200,43 +12508,43 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>145</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
       <c r="J5" s="7" t="s">
-        <v>428</v>
+        <v>446</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>429</v>
+        <v>447</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>208</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
@@ -12246,17 +12554,17 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>431</v>
+        <v>449</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>432</v>
+        <v>450</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
@@ -12266,41 +12574,41 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>433</v>
+        <v>451</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>434</v>
+        <v>452</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
       <c r="J8" s="8" t="s">
-        <v>436</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
@@ -12348,16 +12656,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>125</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>441</v>
+        <v>459</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>25</v>
@@ -12373,13 +12681,13 @@
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="8" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>444</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -12422,351 +12730,351 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>70</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>446</v>
+        <v>464</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>449</v>
+        <v>467</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>450</v>
+        <v>468</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>452</v>
+        <v>470</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>454</v>
+        <v>472</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>455</v>
+        <v>473</v>
       </c>
       <c r="G2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>456</v>
+        <v>474</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>452</v>
+        <v>470</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>454</v>
+        <v>472</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>458</v>
+        <v>476</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>460</v>
+        <v>478</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>463</v>
+        <v>481</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>455</v>
+        <v>473</v>
       </c>
       <c r="G4" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>466</v>
+        <v>484</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>463</v>
+        <v>481</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>467</v>
+        <v>485</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>468</v>
+        <v>486</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>469</v>
+        <v>487</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>470</v>
+        <v>488</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>471</v>
+        <v>489</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>472</v>
+        <v>490</v>
       </c>
       <c r="G6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>474</v>
+        <v>492</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>471</v>
+        <v>489</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>476</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>477</v>
+        <v>495</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>478</v>
+        <v>496</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>471</v>
+        <v>489</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="B9" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>480</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>462</v>
-      </c>
       <c r="D9" s="8" t="s">
-        <v>481</v>
+        <v>499</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>483</v>
+        <v>501</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>484</v>
+        <v>502</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>481</v>
+        <v>499</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="G10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>485</v>
+        <v>503</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>486</v>
+        <v>504</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>471</v>
+        <v>489</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>487</v>
+        <v>505</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>488</v>
+        <v>506</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>231</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>467</v>
+        <v>485</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>490</v>
+        <v>508</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>491</v>
+        <v>509</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>492</v>
+        <v>510</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>231</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>467</v>
+        <v>485</v>
       </c>
       <c r="G13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>493</v>
+        <v>511</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>85</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>455</v>
+        <v>473</v>
       </c>
       <c r="G14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>496</v>
+        <v>514</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>85</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>497</v>
+        <v>515</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>498</v>
+        <v>516</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>499</v>
+        <v>517</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>500</v>
+        <v>518</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>85</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>467</v>
+        <v>485</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>112</v>
@@ -12774,25 +13082,25 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>501</v>
+        <v>519</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>502</v>
+        <v>520</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>85</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>497</v>
+        <v>515</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>498</v>
+        <v>516</v>
       </c>
     </row>
   </sheetData>
@@ -15390,7 +15698,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="10"/>
@@ -15617,7 +15925,7 @@
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="8" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="K6" s="8" t="s">
         <v>338</v>
@@ -15642,10 +15950,10 @@
         <v>340</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>341</v>
+        <v>89</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>225</v>
+        <v>89</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>89</v>
@@ -15654,15 +15962,11 @@
       <c r="J7" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="K7" s="8" t="s">
-        <v>342</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>326</v>
-      </c>
+      <c r="K7" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
@@ -15675,10 +15979,10 @@
         <v>46</v>
       </c>
       <c r="D8" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>343</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>344</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>89</v>
@@ -15691,10 +15995,10 @@
       </c>
       <c r="I8" s="7"/>
       <c r="J8" s="8" t="s">
-        <v>345</v>
+        <v>320</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
@@ -15710,16 +16014,16 @@
         <v>46</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>349</v>
+        <v>89</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>225</v>
+        <v>89</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>89</v>
@@ -15729,142 +16033,140 @@
         <v>334</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>350</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="M9" s="7" t="s">
-        <v>326</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>45</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>317</v>
+        <v>348</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>318</v>
+        <v>349</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>319</v>
+        <v>350</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="I10" s="7"/>
+        <v>351</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>352</v>
+      </c>
       <c r="J10" s="8" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>321</v>
+        <v>353</v>
       </c>
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>45</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>323</v>
+        <v>354</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>355</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>324</v>
+        <v>89</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>225</v>
+        <v>89</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>89</v>
       </c>
       <c r="I11" s="7"/>
       <c r="J11" s="8" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="L11" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>326</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>45</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>328</v>
+        <v>358</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>329</v>
+        <v>359</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>89</v>
+        <v>225</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>89</v>
       </c>
       <c r="I12" s="7"/>
       <c r="J12" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
+        <v>334</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>326</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>45</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>331</v>
+        <v>361</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>332</v>
+        <v>362</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>333</v>
+        <v>89</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>89</v>
@@ -15874,35 +16176,35 @@
       </c>
       <c r="I13" s="7"/>
       <c r="J13" s="8" t="s">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>335</v>
+        <v>364</v>
       </c>
       <c r="L13" s="7"/>
       <c r="M13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>45</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>336</v>
+        <v>365</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>337</v>
+        <v>366</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>89</v>
+        <v>367</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>89</v>
+        <v>225</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>89</v>
@@ -15912,10 +16214,14 @@
         <v>334</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
+        <v>368</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>326</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
@@ -15928,33 +16234,29 @@
         <v>54</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>339</v>
+        <v>317</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>340</v>
+        <v>318</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>341</v>
+        <v>319</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>225</v>
+        <v>89</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>89</v>
       </c>
       <c r="I15" s="7"/>
       <c r="J15" s="8" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>342</v>
-      </c>
-      <c r="L15" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="M15" s="7" t="s">
-        <v>326</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
@@ -15967,29 +16269,33 @@
         <v>54</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>344</v>
+        <v>322</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>323</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>89</v>
+        <v>324</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>89</v>
+        <v>225</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>89</v>
       </c>
       <c r="I16" s="7"/>
       <c r="J16" s="8" t="s">
-        <v>345</v>
+        <v>320</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
+        <v>325</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>326</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
@@ -16002,31 +16308,387 @@
         <v>54</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>347</v>
+        <v>327</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>348</v>
+        <v>328</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>225</v>
+        <v>89</v>
       </c>
       <c r="H17" s="8" t="s">
         <v>89</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="I18" s="7"/>
+      <c r="J18" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="K17" s="8" t="s">
+      <c r="K18" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="I19" s="7"/>
+      <c r="J19" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="I20" s="7"/>
+      <c r="J20" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="I21" s="7"/>
+      <c r="J21" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="I22" s="7"/>
+      <c r="J22" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="F23" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="L17" s="7" t="s">
+      <c r="G23" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="I24" s="7"/>
+      <c r="J24" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="I25" s="7"/>
+      <c r="J25" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="L25" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="M17" s="7" t="s">
+      <c r="M25" s="7" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="I26" s="7"/>
+      <c r="J26" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="I27" s="7"/>
+      <c r="J27" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="M27" s="7" t="s">
         <v>326</v>
       </c>
     </row>
@@ -16037,7 +16699,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="목록에 있는 값만 입력할 수 있습니다" errorStyle="stop" errorTitle="목록에서 선택" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D2:D500" type="list">
-      <formula1>"children_product,kc,trademark_license,parallel_import,customs,labeling,channel_policy,return_policy"</formula1>
+      <formula1>"children_product,kc,trademark_license,parallel_import,copyright_import,design_right,customs_ip_watch,platform_ip_report,listing_assets,customs,labeling,channel_policy,return_policy"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="목록에 있는 값만 입력할 수 있습니다" errorStyle="stop" errorTitle="목록에서 선택" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G2:G500" type="list">
@@ -16083,206 +16745,206 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>354</v>
+        <v>372</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>357</v>
+        <v>375</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>33</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="7"/>
       <c r="F2" s="8" t="s">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="I2" s="7"/>
       <c r="J2" s="8" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="8" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="I3" s="7"/>
       <c r="J3" s="7" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>375</v>
+        <v>393</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>59</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>381</v>
+        <v>399</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>383</v>
+        <v>401</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>387</v>
+        <v>405</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>388</v>
+        <v>406</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="I5" s="7" t="s">
         <v>59</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>391</v>
+        <v>409</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>59</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="8" t="s">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
     </row>
   </sheetData>
